--- a/feedback_surveys/016_net_promoter_score_nps_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/016_net_promoter_score_nps_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Open Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Open Comments 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Open Comments 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Open Comments 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reason for not recommending</t>
+          <t>Demographic Questions 13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Likely'}</t>
+          <t>Extremely Likely</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Executive'}</t>
+          <t>Executive</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'non-executive'}</t>
+          <t>non-executive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Executive'}</t>
+          <t>Non-Executive</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'customer_support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Development'}</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'ceo/founder'}</t>
+          <t>ceo/founder</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'CEO/Founder'}</t>
+          <t>CEO/Founder</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'non-executive'}</t>
+          <t>non-executive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Executive'}</t>
+          <t>Non-Executive</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>demographic_questions_5_choices</t>
+          <t>demographic_questions_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'non-executive'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Executive'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_year'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 year'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '1-2 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '2-5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>demographic_questions_6_choices</t>
+          <t>demographic_questions_7_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5_years'}</t>
+          <t>1_time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5 years'}</t>
+          <t>1 time</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'1_time'}</t>
+          <t>2-5_times</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': '1 time'}</t>
+          <t>2-5 times</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_times'}</t>
+          <t>more_than_5_times</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': '2-5 times'}</t>
+          <t>More than 5 times</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>demographic_questions_7_choices</t>
+          <t>demographic_questions_8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5_times'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5 times'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>demographic_questions_8_choices</t>
+          <t>demographic_questions_9_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>demographic_questions_9_choices</t>
+          <t>demographic_questions_10_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>somewhat_poor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Somewhat Poor</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_poor'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Poor'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>demographic_questions_10_choices</t>
+          <t>demographic_questions_11_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>demographic_questions_11_choices</t>
+          <t>demographic_questions_12_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>demographic_questions_12_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'label':_'extremely_likely'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'label': 'Extremely Likely'}</t>
+          <t>Extremely Likely</t>
         </is>
       </c>
     </row>
